--- a/final_outputs/excel_tables/table_qr_quantile_diff.xlsx
+++ b/final_outputs/excel_tables/table_qr_quantile_diff.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0.732</v>
+        <v>0.83</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.4e-05</v>
+        <v>0.000267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.878</v>
+        <v>0.388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,14 +521,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.000395</v>
+        <v>0.0005509999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.174</v>
+        <v>0.048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.000177</v>
+        <v>0.000599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.736</v>
+        <v>0.432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.000369</v>
+        <v>8.4e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.418</v>
+        <v>0.854</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.1e-05</v>
+        <v>-1.6e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.3e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.968</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.000711</v>
+        <v>0.000476</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.000759</v>
+        <v>0.000393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.426</v>
+        <v>0.648</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.000177</v>
+        <v>6.3e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.732</v>
+        <v>0.962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -713,14 +713,14 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-9e-06</v>
+        <v>-1.8e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>0.214</v>
+        <v>0.042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.1e-05</v>
+        <v>-0.000228</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.000317</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.204</v>
+        <v>0.958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.0005820000000000001</v>
+        <v>-0.000207</v>
       </c>
       <c r="E15" t="n">
-        <v>0.226</v>
+        <v>0.87</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.000193</v>
+        <v>-2.1e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0.55</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>

--- a/final_outputs/excel_tables/table_qr_quantile_diff.xlsx
+++ b/final_outputs/excel_tables/table_qr_quantile_diff.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0.83</v>
+        <v>0.628</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.000267</v>
+        <v>-0.000129</v>
       </c>
       <c r="E3" t="n">
-        <v>0.388</v>
+        <v>0.742</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,14 +521,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0005509999999999999</v>
+        <v>-3e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.048</v>
+        <v>0.984</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.000599</v>
+        <v>-0.00098</v>
       </c>
       <c r="E5" t="n">
-        <v>0.432</v>
+        <v>0.406</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.4e-05</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.854</v>
+        <v>0.152</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.6e-05</v>
+        <v>-1e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4e-05</v>
+        <v>-4e-05</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.000476</v>
+        <v>0.000563</v>
       </c>
       <c r="E9" t="n">
-        <v>0.368</v>
+        <v>0.272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.000393</v>
+        <v>0.000113</v>
       </c>
       <c r="E10" t="n">
-        <v>0.648</v>
+        <v>0.908</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.3e-05</v>
+        <v>0.0005330000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.962</v>
+        <v>0.328</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -713,14 +713,14 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.8e-05</v>
+        <v>-6e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>0.042</v>
+        <v>0.416</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.000228</v>
+        <v>8.899999999999999e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>0.504</v>
+        <v>0.754</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-7.4e-05</v>
+        <v>0.000593</v>
       </c>
       <c r="E14" t="n">
-        <v>0.958</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.000207</v>
+        <v>0.001093</v>
       </c>
       <c r="E15" t="n">
-        <v>0.87</v>
+        <v>0.068</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.1e-05</v>
+        <v>-0.000241</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
